--- a/UTCUTS/B1_Default_Param.xlsx
+++ b/UTCUTS/B1_Default_Param.xlsx
@@ -1175,7 +1175,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FE19FFC-112F-4629-ACCA-3C8DF1306097}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8866919C-DC8F-4C20-9DCC-BA23F06C80DE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
